--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tonsberg_Sandefjord.xls.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Getaround_leiebil_Tonsberg_Sandefjord.xls.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{BDD7FE9B-B2D2-464A-8860-42941A399592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7FE4A70-B3D4-4133-A38F-9E9B5871B183}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{BDD7FE9B-B2D2-464A-8860-42941A399592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{222E5D53-4C75-4EA5-8E89-1098137092AE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B856B024-48C7-4BFF-B5E4-3C408E652A68}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4803" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4839" uniqueCount="103">
   <si>
     <t>CAR_ID</t>
   </si>
@@ -339,6 +339,12 @@
   </si>
   <si>
     <t>Gliwice</t>
+  </si>
+  <si>
+    <t>Horten</t>
+  </si>
+  <si>
+    <t>kraków</t>
   </si>
 </sst>
 </file>
@@ -761,7 +767,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA55DC7-B8AA-4BA7-B767-B74C300660C5}">
-  <dimension ref="A1:J1604"/>
+  <dimension ref="A1:J1616"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="40.28515625" customWidth="1"/>
@@ -34918,7 +34924,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1312" spans="1:8" ht="27" thickBot="1">
+    <row r="1312" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1312" s="2">
         <v>1500032</v>
       </c>
@@ -34944,7 +34950,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="1313" spans="1:8" ht="27" thickBot="1">
+    <row r="1313" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1313" s="2">
         <v>1500032</v>
       </c>
@@ -34970,7 +34976,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="1314" spans="1:8" ht="27" thickBot="1">
+    <row r="1314" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1314" s="2">
         <v>1500032</v>
       </c>
@@ -34996,7 +35002,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="1315" spans="1:8" ht="27" thickBot="1">
+    <row r="1315" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1315" s="2">
         <v>1500032</v>
       </c>
@@ -35022,7 +35028,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="1316" spans="1:8" ht="27" thickBot="1">
+    <row r="1316" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1316" s="2">
         <v>1500032</v>
       </c>
@@ -35048,7 +35054,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="1317" spans="1:8" ht="27" thickBot="1">
+    <row r="1317" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1317" s="2">
         <v>1500032</v>
       </c>
@@ -35074,7 +35080,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="1318" spans="1:8" ht="27" thickBot="1">
+    <row r="1318" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1318" s="2">
         <v>1500032</v>
       </c>
@@ -35100,7 +35106,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="1319" spans="1:8" ht="27" thickBot="1">
+    <row r="1319" spans="1:8" ht="15.75" thickBot="1">
       <c r="A1319" s="2">
         <v>1522893</v>
       </c>
@@ -42534,6 +42540,318 @@
       </c>
       <c r="H1604" s="1" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1605" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1605" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1605" s="2">
+        <v>9754200</v>
+      </c>
+      <c r="D1605" s="2">
+        <v>7322916</v>
+      </c>
+      <c r="E1605" s="5">
+        <v>45975.958333333336</v>
+      </c>
+      <c r="F1605" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1605" s="2">
+        <v>34</v>
+      </c>
+      <c r="H1605" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1606" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1606" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1606" s="2">
+        <v>9744895</v>
+      </c>
+      <c r="D1606" s="2">
+        <v>7315107</v>
+      </c>
+      <c r="E1606" s="5">
+        <v>45968.958333333336</v>
+      </c>
+      <c r="F1606" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1606" s="2">
+        <v>25</v>
+      </c>
+      <c r="H1606" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1607" s="2">
+        <v>1499104</v>
+      </c>
+      <c r="B1607" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1607" s="2">
+        <v>9755787</v>
+      </c>
+      <c r="D1607" s="2">
+        <v>7324179</v>
+      </c>
+      <c r="E1607" s="5">
+        <v>45975.958333333336</v>
+      </c>
+      <c r="F1607" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1607" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1607" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1608" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1608" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1608" s="2">
+        <v>9729255</v>
+      </c>
+      <c r="D1608" s="2">
+        <v>7273084</v>
+      </c>
+      <c r="E1608" s="5">
+        <v>45962.458333333336</v>
+      </c>
+      <c r="F1608" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1608" s="2">
+        <v>27</v>
+      </c>
+      <c r="H1608" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1609" s="2">
+        <v>1314027</v>
+      </c>
+      <c r="B1609" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1609" s="2">
+        <v>9762389</v>
+      </c>
+      <c r="D1609" s="2">
+        <v>7309312</v>
+      </c>
+      <c r="E1609" s="5">
+        <v>45981.958333333336</v>
+      </c>
+      <c r="F1609" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1609" s="2">
+        <v>40</v>
+      </c>
+      <c r="H1609" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1610" s="2">
+        <v>1314027</v>
+      </c>
+      <c r="B1610" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1610" s="2">
+        <v>9777135</v>
+      </c>
+      <c r="D1610" s="2">
+        <v>4952403</v>
+      </c>
+      <c r="E1610" s="5">
+        <v>45985.958333333336</v>
+      </c>
+      <c r="F1610" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1610" s="2">
+        <v>39</v>
+      </c>
+      <c r="H1610" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1611" s="2">
+        <v>1522893</v>
+      </c>
+      <c r="B1611" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1611" s="2">
+        <v>9756011</v>
+      </c>
+      <c r="D1611" s="2">
+        <v>7324272</v>
+      </c>
+      <c r="E1611" s="5">
+        <v>45976.958333333336</v>
+      </c>
+      <c r="F1611" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1611" s="2">
+        <v>42</v>
+      </c>
+      <c r="H1611" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1612" s="2">
+        <v>1500032</v>
+      </c>
+      <c r="B1612" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1612" s="2">
+        <v>9771880</v>
+      </c>
+      <c r="D1612" s="2">
+        <v>4707238</v>
+      </c>
+      <c r="E1612" s="5">
+        <v>45983.958333333336</v>
+      </c>
+      <c r="F1612" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1612" s="2">
+        <v>29</v>
+      </c>
+      <c r="H1612" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1613" s="2">
+        <v>1313901</v>
+      </c>
+      <c r="B1613" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1613" s="2">
+        <v>9717941</v>
+      </c>
+      <c r="D1613" s="2">
+        <v>7291918</v>
+      </c>
+      <c r="E1613" s="5">
+        <v>45962.958333333336</v>
+      </c>
+      <c r="F1613" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1613" s="2">
+        <v>28</v>
+      </c>
+      <c r="H1613" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1614" s="2">
+        <v>1522893</v>
+      </c>
+      <c r="B1614" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1614" s="2">
+        <v>9765980</v>
+      </c>
+      <c r="D1614" s="2">
+        <v>7044484</v>
+      </c>
+      <c r="E1614" s="5">
+        <v>45980.458333333336</v>
+      </c>
+      <c r="F1614" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1614" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1614" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1615" s="2">
+        <v>1522893</v>
+      </c>
+      <c r="B1615" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1615" s="2">
+        <v>9742630</v>
+      </c>
+      <c r="D1615" s="2">
+        <v>7044484</v>
+      </c>
+      <c r="E1615" s="5">
+        <v>45968.458333333336</v>
+      </c>
+      <c r="F1615" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1615" s="2">
+        <v>61</v>
+      </c>
+      <c r="H1615" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:8" ht="15.75" thickBot="1">
+      <c r="A1616" s="2">
+        <v>1499104</v>
+      </c>
+      <c r="B1616" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1616" s="2">
+        <v>9729989</v>
+      </c>
+      <c r="D1616" s="2">
+        <v>7191943</v>
+      </c>
+      <c r="E1616" s="5">
+        <v>45962.458333333336</v>
+      </c>
+      <c r="F1616" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1616" s="2">
+        <v>52</v>
+      </c>
+      <c r="H1616" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
